--- a/BD/ACT_Activos_355_SINTETICO.xlsx
+++ b/BD/ACT_Activos_355_SINTETICO.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>05+380</t>
+          <t>01+269</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -533,7 +533,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.094223, -73.694400</t>
+          <t>5.097823, -73.714200</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -550,7 +550,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -582,7 +584,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07+917</t>
+          <t>03+806</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -590,7 +592,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.092022, -73.681107</t>
+          <t>5.095622, -73.700907</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -607,7 +609,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -639,7 +643,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10+455</t>
+          <t>06+344</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -647,7 +651,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.090897, -73.670410</t>
+          <t>5.094497, -73.690210</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -664,7 +668,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -696,7 +702,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12+992</t>
+          <t>08+882</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -704,7 +710,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.088248, -73.657713</t>
+          <t>5.091848, -73.677513</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -721,7 +727,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -753,7 +761,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15+530</t>
+          <t>11+419</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -761,7 +769,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.085370, -73.644520</t>
+          <t>5.088970, -73.664320</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -778,7 +786,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -810,7 +820,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18+068</t>
+          <t>13+957</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -818,7 +828,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.083696, -73.632187</t>
+          <t>5.087296, -73.651987</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -835,7 +845,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -867,7 +879,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20+605</t>
+          <t>16+494</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -875,7 +887,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.081112, -73.619791</t>
+          <t>5.084712, -73.639591</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -892,7 +904,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -924,7 +938,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23+143</t>
+          <t>19+032</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -932,7 +946,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.078318, -73.608344</t>
+          <t>5.082718, -73.628544</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -949,7 +963,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -981,7 +997,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25+680</t>
+          <t>21+570</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -989,7 +1005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.070322, -73.591769</t>
+          <t>5.081389, -73.615302</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1006,7 +1022,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1038,7 +1056,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28+218</t>
+          <t>24+107</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1046,7 +1064,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.060408, -73.577690</t>
+          <t>5.074808, -73.602890</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1063,7 +1081,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1095,7 +1115,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30+756</t>
+          <t>26+645</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1103,7 +1123,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.052329, -73.560507</t>
+          <t>5.066729, -73.585707</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1120,7 +1140,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1152,7 +1174,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33+293</t>
+          <t>29+182</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1160,7 +1182,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.044609, -73.545053</t>
+          <t>5.059009, -73.570253</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1177,7 +1199,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1205,11 +1229,11 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35+831</t>
+          <t>31+720</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1217,7 +1241,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.033811, -73.529336</t>
+          <t>5.048211, -73.554536</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1234,7 +1258,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1266,7 +1292,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38+368</t>
+          <t>34+258</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1274,7 +1300,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.026824, -73.513847</t>
+          <t>5.041224, -73.539047</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1291,7 +1317,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1323,7 +1351,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40+906</t>
+          <t>36+795</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1331,7 +1359,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.017129, -73.498392</t>
+          <t>5.031529, -73.523592</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1348,7 +1376,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1380,7 +1410,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43+444</t>
+          <t>39+333</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1388,7 +1418,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.008972, -73.482661</t>
+          <t>5.023372, -73.507861</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1405,7 +1435,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1437,7 +1469,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45+981</t>
+          <t>41+870</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1445,7 +1477,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.998834, -73.465904</t>
+          <t>5.014034, -73.492037</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1462,7 +1494,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1494,7 +1528,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48+519</t>
+          <t>44+408</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1502,7 +1536,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.982448, -73.442789</t>
+          <t>5.004315, -73.476700</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1519,7 +1553,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1551,7 +1587,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51+056</t>
+          <t>46+945</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1559,7 +1595,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.967957, -73.419629</t>
+          <t>4.993157, -73.457429</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1576,7 +1612,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1608,7 +1646,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53+594</t>
+          <t>49+483</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1616,7 +1654,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.950598, -73.397117</t>
+          <t>4.975798, -73.434917</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1633,7 +1671,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1665,7 +1705,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56+132</t>
+          <t>52+021</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1673,7 +1713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.936637, -73.374849</t>
+          <t>4.961837, -73.412649</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1690,7 +1730,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1722,7 +1764,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>58+669</t>
+          <t>54+558</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1730,7 +1772,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.921317, -73.350126</t>
+          <t>4.946517, -73.387926</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1747,7 +1789,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1779,7 +1823,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61+207</t>
+          <t>57+096</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1787,7 +1831,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.903976, -73.326611</t>
+          <t>4.929176, -73.364411</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1804,7 +1848,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1836,7 +1882,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>63+744</t>
+          <t>59+633</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1844,7 +1890,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.888048, -73.304672</t>
+          <t>4.913248, -73.342472</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1861,7 +1907,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1893,7 +1941,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>66+282</t>
+          <t>62+171</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1901,7 +1949,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.873038, -73.281672</t>
+          <t>4.898238, -73.319472</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1918,7 +1966,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -1946,11 +1996,11 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>68+820</t>
+          <t>64+709</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1958,7 +2008,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.859928, -73.258648</t>
+          <t>4.883795, -73.294848</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1975,7 +2025,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2003,11 +2055,11 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>71+357</t>
+          <t>67+246</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2015,7 +2067,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.854374, -73.249568</t>
+          <t>4.867129, -73.272435</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2032,7 +2084,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2064,7 +2118,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>73+895</t>
+          <t>69+784</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2072,7 +2126,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.849864, -73.239721</t>
+          <t>4.857064, -73.255921</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2089,7 +2143,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2121,7 +2177,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>76+432</t>
+          <t>72+321</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2129,7 +2185,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.846697, -73.227721</t>
+          <t>4.853897, -73.243921</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2146,7 +2202,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2178,7 +2236,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>78+970</t>
+          <t>74+859</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2186,7 +2244,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.840424, -73.219576</t>
+          <t>4.847624, -73.235776</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2203,7 +2261,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2235,7 +2295,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>81+507</t>
+          <t>77+397</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2243,7 +2303,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.836762, -73.207516</t>
+          <t>4.843962, -73.223716</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2260,7 +2320,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>4</v>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2292,7 +2354,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>84+045</t>
+          <t>79+934</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2300,7 +2362,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.832068, -73.197672</t>
+          <t>4.839268, -73.213872</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2317,7 +2379,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2349,7 +2413,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>86+583</t>
+          <t>82+472</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2357,7 +2421,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.827896, -73.188806</t>
+          <t>4.835096, -73.205006</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2374,7 +2438,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2406,7 +2472,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>89+120</t>
+          <t>85+009</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2414,7 +2480,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.824410, -73.179994</t>
+          <t>4.831610, -73.196194</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2431,7 +2497,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2463,7 +2531,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>91+658</t>
+          <t>87+547</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2471,7 +2539,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.818818, -73.168502</t>
+          <t>4.825818, -73.185502</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2488,7 +2556,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2520,7 +2590,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>94+195</t>
+          <t>90+085</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2528,7 +2598,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.818032, -73.150470</t>
+          <t>4.823366, -73.174137</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2545,7 +2615,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2577,7 +2649,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>96+733</t>
+          <t>92+622</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2585,7 +2657,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.812896, -73.133381</t>
+          <t>4.817396, -73.160381</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2602,7 +2674,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>4</v>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2634,7 +2708,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>99+271</t>
+          <t>95+160</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2642,7 +2716,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.811459, -73.117318</t>
+          <t>4.815959, -73.144318</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2659,7 +2733,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>4</v>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2691,7 +2767,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>101+808</t>
+          <t>97+697</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2699,7 +2775,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.808262, -73.100389</t>
+          <t>4.812762, -73.127389</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2716,7 +2792,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2744,11 +2822,11 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>104+346</t>
+          <t>100+235</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2756,7 +2834,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.806037, -73.084045</t>
+          <t>4.810537, -73.111045</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2773,7 +2851,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>4</v>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2805,7 +2885,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>106+883</t>
+          <t>102+773</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2813,7 +2893,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.802338, -73.067132</t>
+          <t>4.806838, -73.094132</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2830,7 +2910,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2862,7 +2944,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>109+421</t>
+          <t>105+310</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2870,7 +2952,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.799404, -73.051934</t>
+          <t>4.803904, -73.078934</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2887,7 +2969,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2919,7 +3003,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>111+959</t>
+          <t>107+848</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2927,7 +3011,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.796341, -73.034132</t>
+          <t>4.800841, -73.061132</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2944,7 +3028,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>4</v>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -2976,7 +3062,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>114+496</t>
+          <t>110+385</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2984,7 +3070,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.795043, -73.017649</t>
+          <t>4.799410, -73.044249</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3001,7 +3087,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3033,7 +3121,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>117+034</t>
+          <t>112+923</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3041,7 +3129,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.794418, -73.004934</t>
+          <t>4.797673, -73.028201</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3058,7 +3146,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>4</v>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3090,7 +3180,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>119+571</t>
+          <t>115+460</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3098,7 +3188,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.792020, -72.990583</t>
+          <t>4.794720, -73.012183</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3115,7 +3205,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3147,7 +3239,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>122+109</t>
+          <t>117+998</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3155,7 +3247,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.788555, -72.978495</t>
+          <t>4.791255, -73.000095</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3172,7 +3264,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>4</v>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3204,7 +3298,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>124+647</t>
+          <t>120+536</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3212,7 +3306,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.788744, -72.965711</t>
+          <t>4.791444, -72.987311</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3229,7 +3323,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>4</v>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3261,7 +3357,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>127+184</t>
+          <t>123+073</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3269,7 +3365,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.785752, -72.950453</t>
+          <t>4.788452, -72.972053</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3286,7 +3382,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>4</v>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3318,7 +3416,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>129+722</t>
+          <t>125+611</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3326,7 +3424,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.785993, -72.937450</t>
+          <t>4.788693, -72.959050</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3343,7 +3441,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>4</v>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3375,7 +3475,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>132+259</t>
+          <t>128+148</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3383,7 +3483,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.782829, -72.925087</t>
+          <t>4.785529, -72.946687</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3400,7 +3500,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>4</v>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3432,7 +3534,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>134+797</t>
+          <t>130+686</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3440,7 +3542,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.781719, -72.911543</t>
+          <t>4.784419, -72.933143</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3457,7 +3559,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>4</v>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3485,11 +3589,11 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>00+305</t>
+          <t>133+224</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3497,7 +3601,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5.099292, -73.717849</t>
+          <t>4.782059, -72.919316</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3514,7 +3618,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>4</v>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3542,11 +3648,11 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>02+842</t>
+          <t>135+761</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3554,7 +3660,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5.098749, -73.706949</t>
+          <t>4.782071, -72.907305</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3571,7 +3677,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>4</v>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3603,7 +3711,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10+857</t>
+          <t>06+746</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3611,7 +3719,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5.089269, -73.666594</t>
+          <t>5.092869, -73.686394</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3628,7 +3736,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>6</v>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3660,7 +3770,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>16+127</t>
+          <t>12+016</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3668,7 +3778,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5.086282, -73.643327</t>
+          <t>5.089882, -73.663127</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3685,7 +3795,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>6</v>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3717,7 +3829,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>21+398</t>
+          <t>17+287</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3725,7 +3837,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5.081130, -73.616000</t>
+          <t>5.084730, -73.635800</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3742,7 +3854,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>6</v>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3774,7 +3888,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>26+668</t>
+          <t>22+557</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3782,7 +3896,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5.066569, -73.585513</t>
+          <t>5.080231, -73.610344</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3799,7 +3913,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>6</v>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3831,7 +3947,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>31+939</t>
+          <t>27+828</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3839,7 +3955,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5.048354, -73.554988</t>
+          <t>5.062754, -73.580188</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3856,7 +3972,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="n">
+        <v>6</v>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3884,11 +4002,11 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>37+209</t>
+          <t>33+098</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3896,7 +4014,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5.030559, -73.521872</t>
+          <t>5.044959, -73.547072</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3913,7 +4031,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>6</v>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -3945,7 +4065,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>42+479</t>
+          <t>38+368</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3953,7 +4073,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5.010809, -73.488865</t>
+          <t>5.025209, -73.514065</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3970,7 +4090,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>6</v>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4002,7 +4124,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>47+750</t>
+          <t>43+639</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -4010,7 +4132,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.986806, -73.451042</t>
+          <t>5.006652, -73.482596</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4027,7 +4149,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="n">
+        <v>6</v>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4059,7 +4183,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>53+020</t>
+          <t>48+909</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4067,7 +4191,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.954440, -73.402572</t>
+          <t>4.979640, -73.440372</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4084,7 +4208,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>6</v>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4116,7 +4242,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>58+290</t>
+          <t>54+180</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4124,7 +4250,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.923170, -73.354952</t>
+          <t>4.948370, -73.392752</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4141,7 +4267,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>6</v>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4173,7 +4301,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>63+561</t>
+          <t>59+450</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4181,7 +4309,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.890853, -73.304703</t>
+          <t>4.916053, -73.342503</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4198,7 +4326,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>6</v>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4226,11 +4356,11 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>68+831</t>
+          <t>64+720</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4238,7 +4368,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.859246, -73.258210</t>
+          <t>4.883061, -73.294349</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4255,7 +4385,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>6</v>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4287,7 +4419,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>74+102</t>
+          <t>69+991</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4295,7 +4427,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.849777, -73.237388</t>
+          <t>4.856977, -73.253588</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4312,7 +4444,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>6</v>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4344,7 +4478,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>79+372</t>
+          <t>75+261</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4352,7 +4486,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.842156, -73.217551</t>
+          <t>4.849356, -73.233751</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4369,7 +4503,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="n">
+        <v>6</v>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4401,7 +4537,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>84+642</t>
+          <t>80+531</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4409,7 +4545,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.832420, -73.196161</t>
+          <t>4.839620, -73.212361</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4426,7 +4562,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>6</v>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4458,7 +4596,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>89+913</t>
+          <t>85+802</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -4466,7 +4604,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.823101, -73.176680</t>
+          <t>4.830301, -73.192880</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4483,7 +4621,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>6</v>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4515,7 +4655,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>95+183</t>
+          <t>91+072</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4523,7 +4663,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.816776, -73.145304</t>
+          <t>4.821460, -73.171565</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4540,7 +4680,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>6</v>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4572,7 +4714,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>100+454</t>
+          <t>96+343</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4580,7 +4722,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.809058, -73.108956</t>
+          <t>4.813558, -73.135956</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4597,7 +4739,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" t="n">
+        <v>6</v>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4625,11 +4769,11 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>105+724</t>
+          <t>101+613</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4637,7 +4781,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.805165, -73.075376</t>
+          <t>4.809665, -73.102376</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4654,7 +4798,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>6</v>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4686,7 +4832,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>110+994</t>
+          <t>106+883</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4694,7 +4840,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.797589, -73.042188</t>
+          <t>4.802089, -73.069188</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4711,7 +4857,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="n">
+        <v>6</v>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4743,7 +4891,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>116+265</t>
+          <t>112+154</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -4751,7 +4899,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.793173, -73.008206</t>
+          <t>4.796765, -73.032483</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4768,7 +4916,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="n">
+        <v>6</v>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4800,7 +4950,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>121+535</t>
+          <t>117+424</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4808,7 +4958,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.791107, -72.982067</t>
+          <t>4.793807, -73.003667</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4825,7 +4975,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="n">
+        <v>6</v>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4857,7 +5009,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>126+805</t>
+          <t>122+695</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4865,7 +5017,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.785633, -72.952587</t>
+          <t>4.788333, -72.974187</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4882,7 +5034,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" t="n">
+        <v>6</v>
+      </c>
       <c r="N78" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4914,7 +5068,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>132+076</t>
+          <t>127+965</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4922,7 +5076,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.782728, -72.926924</t>
+          <t>4.785428, -72.948524</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4939,7 +5093,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>6</v>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -4967,11 +5123,11 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>00+316</t>
+          <t>133+235</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4979,7 +5135,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5.100467, -73.717591</t>
+          <t>4.783236, -72.919052</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4996,7 +5152,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
+      <c r="M80" t="n">
+        <v>6</v>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5028,7 +5186,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>05+587</t>
+          <t>01+476</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -5036,7 +5194,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>5.095619, -73.693590</t>
+          <t>5.099219, -73.713390</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -5053,7 +5211,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>6</v>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5085,7 +5245,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10+340</t>
+          <t>13+080</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -5093,7 +5253,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5.090983, -73.669219</t>
+          <t>5.088583, -73.656019</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5110,7 +5270,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>5</v>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5142,7 +5304,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>22+797</t>
+          <t>25+537</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5150,7 +5312,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>5.080371, -73.610104</t>
+          <t>5.070880, -73.593359</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5167,7 +5329,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>5</v>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5199,7 +5363,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>35+254</t>
+          <t>37+995</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -5207,7 +5371,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5.037256, -73.533436</t>
+          <t>5.027656, -73.516636</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5224,7 +5388,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>5</v>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5256,7 +5422,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>47+711</t>
+          <t>50+452</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5264,7 +5430,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.987209, -73.450609</t>
+          <t>4.970409, -73.425409</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -5281,7 +5447,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>5</v>
+      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5313,7 +5481,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60+169</t>
+          <t>62+909</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5321,7 +5489,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.911850, -73.336876</t>
+          <t>4.895050, -73.311676</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5338,7 +5506,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>5</v>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5370,7 +5540,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>72+626</t>
+          <t>75+367</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5378,7 +5548,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.852689, -73.243558</t>
+          <t>4.847889, -73.232758</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -5395,7 +5565,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>5</v>
+      </c>
       <c r="N87" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5427,7 +5599,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>85+083</t>
+          <t>87+824</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5435,7 +5607,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.830521, -73.193554</t>
+          <t>4.825721, -73.182754</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5452,7 +5624,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>5</v>
+      </c>
       <c r="N88" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5484,7 +5658,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>97+540</t>
+          <t>100+281</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5492,7 +5666,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.812903, -73.128998</t>
+          <t>4.809903, -73.110998</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5509,7 +5683,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>5</v>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5541,7 +5717,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>109+998</t>
+          <t>112+738</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -5549,7 +5725,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4.800658, -73.046594</t>
+          <t>4.797658, -73.028594</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5566,7 +5742,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>5</v>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5598,7 +5776,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>122+455</t>
+          <t>125+196</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5606,7 +5784,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.790165, -72.975870</t>
+          <t>4.788365, -72.961470</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5623,7 +5801,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>5</v>
+      </c>
       <c r="N91" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5651,11 +5831,11 @@
         <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>134+912</t>
+          <t>00+623</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5663,7 +5843,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.782495, -72.911238</t>
+          <t>5.100558, -73.717111</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5680,7 +5860,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>5</v>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5712,7 +5894,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>03+606</t>
+          <t>10+458</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5720,7 +5902,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>5.096805, -73.701610</t>
+          <t>5.090805, -73.668610</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5737,7 +5919,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>4</v>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5769,7 +5953,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>10+818</t>
+          <t>17+670</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -5777,7 +5961,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>5.089528, -73.667615</t>
+          <t>5.083528, -73.634615</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5794,7 +5978,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
       <c r="N94" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5826,7 +6012,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>18+030</t>
+          <t>24+882</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5834,7 +6020,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5.084575, -73.633522</t>
+          <t>5.073207, -73.597838</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5851,7 +6037,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>4</v>
+      </c>
       <c r="N95" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5883,7 +6071,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>25+242</t>
+          <t>32+094</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5891,7 +6079,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>5.070717, -73.595681</t>
+          <t>5.046717, -73.553681</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5908,7 +6096,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="n">
+        <v>4</v>
+      </c>
       <c r="N96" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5936,11 +6126,11 @@
         <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>32+454</t>
+          <t>39+306</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5948,7 +6138,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.047310, -73.550806</t>
+          <t>5.023310, -73.508806</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5965,7 +6155,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
+      <c r="M97" t="n">
+        <v>4</v>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -5997,7 +6189,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>39+667</t>
+          <t>46+518</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -6005,7 +6197,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>5.019815, -73.507165</t>
+          <t>4.993604, -73.462586</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -6022,7 +6214,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
+      <c r="M98" t="n">
+        <v>4</v>
+      </c>
       <c r="N98" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6054,7 +6248,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>46+879</t>
+          <t>53+730</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -6062,7 +6256,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.993751, -73.459093</t>
+          <t>4.951751, -73.396093</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -6079,7 +6273,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>4</v>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6111,7 +6307,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>54+091</t>
+          <t>60+942</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6119,7 +6315,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.949495, -73.392724</t>
+          <t>4.907495, -73.329724</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -6136,7 +6332,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
+      <c r="M100" t="n">
+        <v>4</v>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6168,7 +6366,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61+303</t>
+          <t>68+154</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6176,7 +6374,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.903789, -73.327548</t>
+          <t>4.861789, -73.264548</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -6193,7 +6391,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
+      <c r="M101" t="n">
+        <v>4</v>
+      </c>
       <c r="N101" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6225,7 +6425,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>68+515</t>
+          <t>75+367</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6233,7 +6433,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.860661, -73.260829</t>
+          <t>4.848661, -73.233829</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -6250,7 +6450,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
+      <c r="M102" t="n">
+        <v>4</v>
+      </c>
       <c r="N102" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6282,7 +6484,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>75+727</t>
+          <t>82+579</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6290,7 +6492,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.847101, -73.231669</t>
+          <t>4.835101, -73.204669</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -6307,7 +6509,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
+      <c r="M103" t="n">
+        <v>4</v>
+      </c>
       <c r="N103" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6339,7 +6543,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>82+939</t>
+          <t>89+791</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6347,7 +6551,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4.833744, -73.203984</t>
+          <t>4.821744, -73.176984</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -6364,7 +6568,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>4</v>
+      </c>
       <c r="N104" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6396,7 +6602,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>90+151</t>
+          <t>97+003</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6404,7 +6610,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.822703, -73.175357</t>
+          <t>4.814413, -73.133515</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -6421,7 +6627,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>4</v>
+      </c>
       <c r="N105" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6449,11 +6657,11 @@
         <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>97+363</t>
+          <t>104+215</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6461,7 +6669,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.813100, -73.130034</t>
+          <t>4.805600, -73.085034</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -6478,7 +6686,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>4</v>
+      </c>
       <c r="N106" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6510,7 +6720,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>104+576</t>
+          <t>111+427</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -6518,7 +6728,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.804442, -73.082033</t>
+          <t>4.796942, -73.037033</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -6535,7 +6745,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>4</v>
+      </c>
       <c r="N107" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6567,7 +6779,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>111+788</t>
+          <t>118+639</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -6575,7 +6787,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.797950, -73.036500</t>
+          <t>4.792397, -72.997343</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6592,7 +6804,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>4</v>
+      </c>
       <c r="N108" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6624,7 +6838,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>118+1000</t>
+          <t>125+851</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -6632,7 +6846,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.793020, -72.995962</t>
+          <t>4.788520, -72.959962</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6649,7 +6863,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>4</v>
+      </c>
       <c r="N109" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6681,7 +6897,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>126+212</t>
+          <t>133+063</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -6689,7 +6905,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.788342, -72.956860</t>
+          <t>4.783842, -72.920860</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6706,7 +6922,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>4</v>
+      </c>
       <c r="N110" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6734,11 +6952,11 @@
         <v>4</v>
       </c>
       <c r="E111" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>133+424</t>
+          <t>03+245</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -6746,7 +6964,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.783377, -72.919294</t>
+          <t>5.098167, -73.704715</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6763,7 +6981,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>4</v>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6820,7 +7040,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>6</v>
+      </c>
       <c r="N112" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6877,7 +7099,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>6</v>
+      </c>
       <c r="N113" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6934,7 +7158,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>6</v>
+      </c>
       <c r="N114" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -6991,7 +7217,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>6</v>
+      </c>
       <c r="N115" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7023,7 +7251,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>18+499</t>
+          <t>17+129</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -7031,7 +7259,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>5.083142, -73.630156</t>
+          <t>5.084342, -73.636756</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -7048,7 +7276,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>7</v>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7080,7 +7310,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>52+757</t>
+          <t>51+386</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -7088,7 +7318,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.955652, -73.404640</t>
+          <t>4.964052, -73.417240</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -7105,7 +7335,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>7</v>
+      </c>
       <c r="N117" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7137,7 +7369,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>87+014</t>
+          <t>85+644</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7145,7 +7377,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.827484, -73.187768</t>
+          <t>4.829884, -73.193168</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -7162,7 +7394,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>7</v>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7194,7 +7428,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>121+272</t>
+          <t>119+901</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7202,7 +7436,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.790489, -72.983827</t>
+          <t>4.791389, -72.991027</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -7219,7 +7453,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>7</v>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7251,7 +7487,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>18+499</t>
+          <t>17+129</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7259,7 +7495,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.084428, -73.631829</t>
+          <t>5.085628, -73.638429</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -7276,7 +7512,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>7</v>
+      </c>
       <c r="N120" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7308,7 +7546,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>52+757</t>
+          <t>51+386</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7316,7 +7554,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.957373, -73.404341</t>
+          <t>4.965773, -73.416941</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -7333,7 +7571,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>7</v>
+      </c>
       <c r="N121" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7365,7 +7605,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>87+014</t>
+          <t>85+644</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7373,7 +7613,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.827117, -73.187937</t>
+          <t>4.829517, -73.193337</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -7390,7 +7630,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>7</v>
+      </c>
       <c r="N122" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7422,7 +7664,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>121+272</t>
+          <t>119+901</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7430,7 +7672,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.790341, -72.983348</t>
+          <t>4.791241, -72.990548</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -7447,7 +7689,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>7</v>
+      </c>
       <c r="N123" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7479,7 +7723,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>23+980</t>
+          <t>22+610</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7487,7 +7731,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>5.075409, -73.603225</t>
+          <t>5.079609, -73.611325</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -7504,7 +7748,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>7</v>
+      </c>
       <c r="N124" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7536,7 +7782,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>58+238</t>
+          <t>56+867</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -7544,7 +7790,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.922420, -73.353701</t>
+          <t>4.930820, -73.366301</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -7561,7 +7807,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>7</v>
+      </c>
       <c r="N125" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7593,7 +7841,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>92+495</t>
+          <t>91+125</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -7601,7 +7849,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.819559, -73.163028</t>
+          <t>4.821209, -73.171428</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -7618,7 +7866,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>7</v>
+      </c>
       <c r="N126" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7650,7 +7900,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>126+753</t>
+          <t>125+382</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -7658,7 +7908,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.785495, -72.952862</t>
+          <t>4.786395, -72.960062</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -7675,7 +7925,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
+      <c r="M127" t="n">
+        <v>7</v>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7732,7 +7984,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>6</v>
+      </c>
       <c r="N128" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7789,7 +8043,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>6</v>
+      </c>
       <c r="N129" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7846,7 +8102,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>6</v>
+      </c>
       <c r="N130" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7903,7 +8161,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>6</v>
+      </c>
       <c r="N131" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -7960,7 +8220,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>6</v>
+      </c>
       <c r="N132" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8017,7 +8279,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>6</v>
+      </c>
       <c r="N133" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8074,7 +8338,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>6</v>
+      </c>
       <c r="N134" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8131,7 +8397,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>6</v>
+      </c>
       <c r="N135" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8188,7 +8456,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>6</v>
+      </c>
       <c r="N136" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8245,7 +8515,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>6</v>
+      </c>
       <c r="N137" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8302,7 +8574,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>6</v>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8359,7 +8633,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>6</v>
+      </c>
       <c r="N139" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8416,7 +8692,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>6</v>
+      </c>
       <c r="N140" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8473,7 +8751,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>6</v>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8530,7 +8810,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>6</v>
+      </c>
       <c r="N142" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8587,7 +8869,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>6</v>
+      </c>
       <c r="N143" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8619,7 +8903,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>22+610</t>
+          <t>21+240</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -8627,7 +8911,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>5.079623, -73.610796</t>
+          <t>5.080823, -73.617396</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -8644,7 +8928,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>6</v>
+      </c>
       <c r="N144" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8676,7 +8962,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>56+867</t>
+          <t>55+497</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -8684,7 +8970,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.930938, -73.367910</t>
+          <t>4.939338, -73.380510</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -8701,7 +8987,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>6</v>
+      </c>
       <c r="N145" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8733,7 +9021,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>91+125</t>
+          <t>89+755</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -8741,7 +9029,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>4.820687, -73.170114</t>
+          <t>4.823087, -73.175514</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -8758,7 +9046,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>6</v>
+      </c>
       <c r="N146" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8790,7 +9080,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>125+382</t>
+          <t>124+012</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -8798,7 +9088,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4.787013, -72.961077</t>
+          <t>4.787913, -72.968277</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -8815,7 +9105,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>6</v>
+      </c>
       <c r="N147" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8847,7 +9139,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>00+483</t>
+          <t>07+334</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -8855,7 +9147,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>5.100375, -73.717232</t>
+          <t>5.094375, -73.684232</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -8872,7 +9164,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>7</v>
+      </c>
       <c r="N148" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8904,7 +9198,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>01+448</t>
+          <t>08+299</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -8912,7 +9206,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>5.098578, -73.713079</t>
+          <t>5.092578, -73.680079</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -8929,7 +9223,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>7</v>
+      </c>
       <c r="N149" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -8961,7 +9257,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>02+413</t>
+          <t>09+264</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -8969,7 +9265,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>5.096748, -73.707794</t>
+          <t>5.090748, -73.674794</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -8986,7 +9282,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>7</v>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9018,7 +9316,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>03+377</t>
+          <t>10+229</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -9026,7 +9324,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>5.097015, -73.704899</t>
+          <t>5.091015, -73.671899</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -9043,7 +9341,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>7</v>
+      </c>
       <c r="N151" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9075,7 +9375,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>04+343</t>
+          <t>11+194</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -9083,7 +9383,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>5.096112, -73.698169</t>
+          <t>5.090112, -73.665169</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -9100,7 +9400,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
+      <c r="M152" t="n">
+        <v>7</v>
+      </c>
       <c r="N152" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9132,7 +9434,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>05+307</t>
+          <t>12+159</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -9140,7 +9442,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>5.095824, -73.694419</t>
+          <t>5.089824, -73.661419</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -9157,7 +9459,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>7</v>
+      </c>
       <c r="N153" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9189,7 +9493,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>06+272</t>
+          <t>13+124</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -9197,7 +9501,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>5.093220, -73.689451</t>
+          <t>5.087220, -73.656451</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -9214,7 +9518,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
+      <c r="M154" t="n">
+        <v>7</v>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9246,7 +9552,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>07+237</t>
+          <t>14+089</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -9254,7 +9560,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>5.092868, -73.685770</t>
+          <t>5.086868, -73.652770</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -9271,7 +9577,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>7</v>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9303,7 +9611,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>08+202</t>
+          <t>15+054</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -9311,7 +9619,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>5.093226, -73.681307</t>
+          <t>5.087226, -73.648307</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -9328,7 +9636,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
+      <c r="M156" t="n">
+        <v>7</v>
+      </c>
       <c r="N156" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9360,7 +9670,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>09+167</t>
+          <t>16+019</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -9368,7 +9678,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>5.092723, -73.676706</t>
+          <t>5.086723, -73.643706</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -9385,7 +9695,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
+      <c r="M157" t="n">
+        <v>7</v>
+      </c>
       <c r="N157" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9417,7 +9729,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>10+133</t>
+          <t>16+984</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -9425,7 +9737,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>5.089974, -73.670457</t>
+          <t>5.083974, -73.637457</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -9442,7 +9754,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
+      <c r="M158" t="n">
+        <v>7</v>
+      </c>
       <c r="N158" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9474,7 +9788,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>11+098</t>
+          <t>17+949</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -9482,7 +9796,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>5.089518, -73.665676</t>
+          <t>5.083518, -73.632676</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -9499,7 +9813,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" t="n">
+        <v>7</v>
+      </c>
       <c r="N159" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9531,7 +9847,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>12+062</t>
+          <t>18+914</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -9539,7 +9855,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>5.089322, -73.661935</t>
+          <t>5.083322, -73.628935</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -9556,7 +9872,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>7</v>
+      </c>
       <c r="N160" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9588,7 +9906,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>13+027</t>
+          <t>19+879</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -9596,7 +9914,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>5.087307, -73.657882</t>
+          <t>5.081307, -73.624882</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -9613,7 +9931,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>7</v>
+      </c>
       <c r="N161" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9645,7 +9965,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>13+992</t>
+          <t>20+844</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -9653,7 +9973,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>5.088699, -73.652697</t>
+          <t>5.082699, -73.619697</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -9670,7 +9990,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
+      <c r="M162" t="n">
+        <v>7</v>
+      </c>
       <c r="N162" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9702,7 +10024,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>14+957</t>
+          <t>21+809</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -9710,7 +10032,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>5.086787, -73.647006</t>
+          <t>5.080787, -73.614006</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -9727,7 +10049,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>7</v>
+      </c>
       <c r="N163" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9759,7 +10083,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>15+922</t>
+          <t>22+774</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -9767,7 +10091,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>5.085975, -73.642642</t>
+          <t>5.079975, -73.609642</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -9784,7 +10108,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
+      <c r="M164" t="n">
+        <v>7</v>
+      </c>
       <c r="N164" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9816,7 +10142,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>16+887</t>
+          <t>23+739</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -9824,7 +10150,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>5.086055, -73.639848</t>
+          <t>5.077688, -73.605665</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -9841,7 +10167,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" t="n">
+        <v>7</v>
+      </c>
       <c r="N165" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9873,7 +10201,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>17+852</t>
+          <t>24+704</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -9881,7 +10209,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>5.085064, -73.633455</t>
+          <t>5.074162, -73.598004</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -9898,7 +10226,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>7</v>
+      </c>
       <c r="N166" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9930,7 +10260,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>18+818</t>
+          <t>25+669</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -9938,7 +10268,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>5.084017, -73.629315</t>
+          <t>5.070580, -73.592596</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -9955,7 +10285,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>7</v>
+      </c>
       <c r="N167" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -9987,7 +10319,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>19+782</t>
+          <t>26+634</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -9995,7 +10327,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>5.081642, -73.623513</t>
+          <t>5.065670, -73.585527</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -10012,7 +10344,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>7</v>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10044,7 +10378,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>20+747</t>
+          <t>27+599</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -10052,7 +10386,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>5.081202, -73.619707</t>
+          <t>5.062695, -73.580453</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -10069,7 +10403,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
+      <c r="M169" t="n">
+        <v>7</v>
+      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10101,7 +10437,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>21+713</t>
+          <t>28+564</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -10109,7 +10445,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>5.080075, -73.616190</t>
+          <t>5.059032, -73.575669</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -10126,7 +10462,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>7</v>
+      </c>
       <c r="N170" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10158,7 +10496,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>22+678</t>
+          <t>29+529</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -10166,7 +10504,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>5.079259, -73.610346</t>
+          <t>5.055681, -73.568557</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -10183,7 +10521,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>7</v>
+      </c>
       <c r="N171" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10215,7 +10555,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>23+642</t>
+          <t>30+494</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -10223,7 +10563,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>5.077285, -73.605906</t>
+          <t>5.053285, -73.563906</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -10240,7 +10580,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>7</v>
+      </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10272,7 +10614,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>24+608</t>
+          <t>31+459</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -10280,7 +10622,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>5.073922, -73.600441</t>
+          <t>5.049922, -73.558441</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -10297,7 +10639,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>7</v>
+      </c>
       <c r="N173" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10329,7 +10673,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>25+573</t>
+          <t>32+424</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -10337,7 +10681,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>5.070749, -73.594202</t>
+          <t>5.046749, -73.552202</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -10354,7 +10698,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>7</v>
+      </c>
       <c r="N174" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10386,7 +10732,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>26+537</t>
+          <t>33+389</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -10394,7 +10740,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>5.067962, -73.587842</t>
+          <t>5.043962, -73.545842</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -10411,7 +10757,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>7</v>
+      </c>
       <c r="N175" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10439,11 +10787,11 @@
         <v>12</v>
       </c>
       <c r="E176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>27+503</t>
+          <t>34+354</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -10451,7 +10799,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>5.063220, -73.582462</t>
+          <t>5.039220, -73.540462</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -10468,7 +10816,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
+      <c r="M176" t="n">
+        <v>7</v>
+      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10496,11 +10846,11 @@
         <v>12</v>
       </c>
       <c r="E177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>28+468</t>
+          <t>35+319</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -10508,7 +10858,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>5.060907, -73.574710</t>
+          <t>5.036907, -73.532710</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -10525,7 +10875,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
+      <c r="M177" t="n">
+        <v>7</v>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10553,11 +10905,11 @@
         <v>12</v>
       </c>
       <c r="E178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>29+432</t>
+          <t>36+284</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -10565,7 +10917,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>5.055818, -73.570288</t>
+          <t>5.031818, -73.528288</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -10582,7 +10934,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>7</v>
+      </c>
       <c r="N178" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10610,11 +10964,11 @@
         <v>12</v>
       </c>
       <c r="E179" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>30+398</t>
+          <t>37+249</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -10622,7 +10976,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>5.053895, -73.564206</t>
+          <t>5.029895, -73.522206</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -10639,7 +10993,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>7</v>
+      </c>
       <c r="N179" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10667,11 +11023,11 @@
         <v>12</v>
       </c>
       <c r="E180" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>31+363</t>
+          <t>38+214</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -10679,7 +11035,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>5.050057, -73.557355</t>
+          <t>5.026057, -73.515355</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -10696,7 +11052,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>7</v>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10724,11 +11082,11 @@
         <v>12</v>
       </c>
       <c r="E181" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>32+328</t>
+          <t>39+179</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -10736,7 +11094,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>5.047587, -73.551517</t>
+          <t>5.023587, -73.509517</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -10753,7 +11111,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>7</v>
+      </c>
       <c r="N181" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10781,11 +11141,11 @@
         <v>12</v>
       </c>
       <c r="E182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>33+293</t>
+          <t>40+144</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -10793,7 +11153,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>5.043119, -73.545577</t>
+          <t>5.019119, -73.503577</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -10810,7 +11170,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>7</v>
+      </c>
       <c r="N182" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10842,7 +11204,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>34+258</t>
+          <t>41+109</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -10850,7 +11212,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>5.039901, -73.540495</t>
+          <t>5.015901, -73.498495</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -10867,7 +11229,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>7</v>
+      </c>
       <c r="N183" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10899,7 +11263,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>35+222</t>
+          <t>42+074</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -10907,7 +11271,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>5.036100, -73.534065</t>
+          <t>5.012100, -73.492065</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -10924,7 +11288,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>7</v>
+      </c>
       <c r="N184" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -10956,7 +11322,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>36+188</t>
+          <t>43+039</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -10964,7 +11330,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>5.033602, -73.528224</t>
+          <t>5.009602, -73.486224</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -10981,7 +11347,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
+      <c r="M185" t="n">
+        <v>7</v>
+      </c>
       <c r="N185" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11013,7 +11381,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>37+153</t>
+          <t>44+004</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -11021,7 +11389,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>5.029174, -73.521565</t>
+          <t>5.005174, -73.479565</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -11038,7 +11406,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>7</v>
+      </c>
       <c r="N186" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11070,7 +11440,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>38+117</t>
+          <t>44+969</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -11078,7 +11448,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>5.027636, -73.516072</t>
+          <t>5.003636, -73.474072</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -11095,7 +11465,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>7</v>
+      </c>
       <c r="N187" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11127,7 +11499,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>39+083</t>
+          <t>45+934</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -11135,7 +11507,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>5.024348, -73.509579</t>
+          <t>4.999672, -73.466790</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -11152,7 +11524,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
+      <c r="M188" t="n">
+        <v>7</v>
+      </c>
       <c r="N188" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11184,7 +11558,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>40+047</t>
+          <t>46+899</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -11192,7 +11566,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>5.019672, -73.504477</t>
+          <t>4.992460, -73.458730</t>
         </is>
       </c>
       <c r="I189" t="n">
@@ -11209,7 +11583,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>7</v>
+      </c>
       <c r="N189" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11241,7 +11617,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>41+012</t>
+          <t>47+864</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -11249,7 +11625,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>5.017066, -73.498146</t>
+          <t>4.987319, -73.449441</t>
         </is>
       </c>
       <c r="I190" t="n">
@@ -11266,7 +11642,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>7</v>
+      </c>
       <c r="N190" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11298,7 +11676,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>41+977</t>
+          <t>48+829</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -11306,7 +11684,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>5.013824, -73.491604</t>
+          <t>4.981542, -73.439942</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -11323,7 +11701,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>7</v>
+      </c>
       <c r="N191" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11355,7 +11735,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>42+943</t>
+          <t>49+794</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -11363,7 +11743,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>5.010806, -73.485930</t>
+          <t>4.975989, -73.431310</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -11380,7 +11760,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>7</v>
+      </c>
       <c r="N192" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11412,7 +11794,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>43+908</t>
+          <t>50+759</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -11420,7 +11802,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>5.005441, -73.480175</t>
+          <t>4.968089, -73.422598</t>
         </is>
       </c>
       <c r="I193" t="n">
@@ -11437,7 +11819,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>7</v>
+      </c>
       <c r="N193" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11469,7 +11853,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>44+873</t>
+          <t>51+724</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -11477,7 +11861,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>5.002571, -73.475288</t>
+          <t>4.962683, -73.414753</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -11494,7 +11878,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>7</v>
+      </c>
       <c r="N194" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11526,7 +11912,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>45+837</t>
+          <t>52+689</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -11534,7 +11920,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>4.999451, -73.467444</t>
+          <t>4.957451, -73.404444</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -11551,7 +11937,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>7</v>
+      </c>
       <c r="N195" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11583,7 +11971,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>46+803</t>
+          <t>53+654</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -11591,7 +11979,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>4.993078, -73.460189</t>
+          <t>4.951078, -73.397189</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -11608,7 +11996,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>7</v>
+      </c>
       <c r="N196" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11640,7 +12030,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>47+767</t>
+          <t>54+619</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -11648,7 +12038,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>4.986602, -73.449663</t>
+          <t>4.944602, -73.386663</t>
         </is>
       </c>
       <c r="I197" t="n">
@@ -11665,7 +12055,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>7</v>
+      </c>
       <c r="N197" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11697,7 +12089,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>48+733</t>
+          <t>55+584</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -11705,7 +12097,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4.980134, -73.440908</t>
+          <t>4.938134, -73.377908</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -11722,7 +12114,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>7</v>
+      </c>
       <c r="N198" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11754,7 +12148,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>49+698</t>
+          <t>56+549</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -11762,7 +12156,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>4.976131, -73.432165</t>
+          <t>4.934131, -73.369165</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -11779,7 +12173,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>7</v>
+      </c>
       <c r="N199" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11811,7 +12207,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>50+663</t>
+          <t>57+514</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -11819,7 +12215,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>4.969908, -73.423342</t>
+          <t>4.927908, -73.360342</t>
         </is>
       </c>
       <c r="I200" t="n">
@@ -11836,7 +12232,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>7</v>
+      </c>
       <c r="N200" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11868,7 +12266,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>51+627</t>
+          <t>58+479</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -11876,7 +12274,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>4.963314, -73.414674</t>
+          <t>4.921314, -73.351674</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -11893,7 +12291,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>7</v>
+      </c>
       <c r="N201" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11925,7 +12325,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>52+593</t>
+          <t>59+444</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -11933,7 +12333,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>4.956737, -73.406941</t>
+          <t>4.914737, -73.343941</t>
         </is>
       </c>
       <c r="I202" t="n">
@@ -11950,7 +12350,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>7</v>
+      </c>
       <c r="N202" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -11982,7 +12384,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>53+557</t>
+          <t>60+409</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -11990,7 +12392,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>4.952529, -73.397230</t>
+          <t>4.910529, -73.334230</t>
         </is>
       </c>
       <c r="I203" t="n">
@@ -12007,7 +12409,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>7</v>
+      </c>
       <c r="N203" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12039,7 +12443,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>54+523</t>
+          <t>61+374</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -12047,7 +12451,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>4.946938, -73.388020</t>
+          <t>4.904938, -73.325020</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -12064,7 +12468,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>7</v>
+      </c>
       <c r="N204" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12096,7 +12502,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>55+488</t>
+          <t>62+339</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -12104,7 +12510,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>4.940700, -73.379111</t>
+          <t>4.898700, -73.316111</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -12121,7 +12527,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
+      <c r="M205" t="n">
+        <v>7</v>
+      </c>
       <c r="N205" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12153,7 +12561,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>56+453</t>
+          <t>63+304</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -12161,7 +12569,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>4.934659, -73.370207</t>
+          <t>4.892659, -73.307207</t>
         </is>
       </c>
       <c r="I206" t="n">
@@ -12178,7 +12586,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>7</v>
+      </c>
       <c r="N206" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12210,7 +12620,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>57+417</t>
+          <t>64+269</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -12218,7 +12628,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>4.927461, -73.361438</t>
+          <t>4.885461, -73.298438</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -12235,7 +12645,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>7</v>
+      </c>
       <c r="N207" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12267,7 +12679,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>58+383</t>
+          <t>65+234</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -12275,7 +12687,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4.921345, -73.353880</t>
+          <t>4.879345, -73.290880</t>
         </is>
       </c>
       <c r="I208" t="n">
@@ -12292,7 +12704,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>7</v>
+      </c>
       <c r="N208" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12324,7 +12738,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>59+347</t>
+          <t>66+199</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -12332,7 +12746,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>4.917094, -73.344924</t>
+          <t>4.875094, -73.281924</t>
         </is>
       </c>
       <c r="I209" t="n">
@@ -12349,7 +12763,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
+      <c r="M209" t="n">
+        <v>7</v>
+      </c>
       <c r="N209" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12381,7 +12797,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60+313</t>
+          <t>67+164</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -12389,7 +12805,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>4.910754, -73.335980</t>
+          <t>4.868754, -73.272980</t>
         </is>
       </c>
       <c r="I210" t="n">
@@ -12406,7 +12822,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>7</v>
+      </c>
       <c r="N210" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12438,7 +12856,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61+278</t>
+          <t>68+129</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -12446,7 +12864,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>4.905375, -73.326188</t>
+          <t>4.863375, -73.263188</t>
         </is>
       </c>
       <c r="I211" t="n">
@@ -12463,7 +12881,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>7</v>
+      </c>
       <c r="N211" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12491,11 +12911,11 @@
         <v>12</v>
       </c>
       <c r="E212" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>62+242</t>
+          <t>69+094</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -12503,7 +12923,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>4.899400, -73.318563</t>
+          <t>4.859935, -73.258605</t>
         </is>
       </c>
       <c r="I212" t="n">
@@ -12520,7 +12940,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
+      <c r="M212" t="n">
+        <v>7</v>
+      </c>
       <c r="N212" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12548,11 +12970,11 @@
         <v>12</v>
       </c>
       <c r="E213" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>63+208</t>
+          <t>70+059</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -12560,7 +12982,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>4.892557, -73.309574</t>
+          <t>4.857317, -73.254687</t>
         </is>
       </c>
       <c r="I213" t="n">
@@ -12577,7 +12999,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
+      <c r="M213" t="n">
+        <v>7</v>
+      </c>
       <c r="N213" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12605,11 +13029,11 @@
         <v>12</v>
       </c>
       <c r="E214" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>64+172</t>
+          <t>71+024</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -12617,7 +13041,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>4.885887, -73.299054</t>
+          <t>4.854873, -73.249237</t>
         </is>
       </c>
       <c r="I214" t="n">
@@ -12634,7 +13058,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>7</v>
+      </c>
       <c r="N214" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12662,11 +13088,11 @@
         <v>12</v>
       </c>
       <c r="E215" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>65+138</t>
+          <t>71+989</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -12674,7 +13100,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>4.881091, -73.291684</t>
+          <t>4.854302, -73.246937</t>
         </is>
       </c>
       <c r="I215" t="n">
@@ -12691,7 +13117,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
+      <c r="M215" t="n">
+        <v>7</v>
+      </c>
       <c r="N215" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12719,11 +13147,11 @@
         <v>12</v>
       </c>
       <c r="E216" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>66+103</t>
+          <t>72+954</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -12731,7 +13159,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>4.873617, -73.281443</t>
+          <t>4.851053, -73.241767</t>
         </is>
       </c>
       <c r="I216" t="n">
@@ -12748,7 +13176,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
+      <c r="M216" t="n">
+        <v>7</v>
+      </c>
       <c r="N216" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12776,11 +13206,11 @@
         <v>12</v>
       </c>
       <c r="E217" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>67+067</t>
+          <t>73+919</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -12788,7 +13218,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>4.868836, -73.272106</t>
+          <t>4.850498, -73.237501</t>
         </is>
       </c>
       <c r="I217" t="n">
@@ -12805,7 +13235,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>7</v>
+      </c>
       <c r="N217" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12833,11 +13265,11 @@
         <v>12</v>
       </c>
       <c r="E218" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>68+032</t>
+          <t>74+884</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -12845,7 +13277,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>4.863983, -73.263861</t>
+          <t>4.849871, -73.234325</t>
         </is>
       </c>
       <c r="I218" t="n">
@@ -12862,7 +13294,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>7</v>
+      </c>
       <c r="N218" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12894,7 +13328,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>68+998</t>
+          <t>75+849</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -12902,7 +13336,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>4.858690, -73.258697</t>
+          <t>4.846690, -73.231697</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -12919,7 +13353,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>7</v>
+      </c>
       <c r="N219" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -12951,7 +13387,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69+963</t>
+          <t>76+814</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -12959,7 +13395,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>4.857227, -73.255096</t>
+          <t>4.845227, -73.228096</t>
         </is>
       </c>
       <c r="I220" t="n">
@@ -12976,7 +13412,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>7</v>
+      </c>
       <c r="N220" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13008,7 +13446,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>70+927</t>
+          <t>77+779</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -13016,7 +13454,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>4.854867, -73.249728</t>
+          <t>4.842867, -73.222728</t>
         </is>
       </c>
       <c r="I221" t="n">
@@ -13033,7 +13471,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
+      <c r="M221" t="n">
+        <v>7</v>
+      </c>
       <c r="N221" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13065,7 +13505,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>71+892</t>
+          <t>78+744</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -13073,7 +13513,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>4.853191, -73.246025</t>
+          <t>4.841191, -73.219025</t>
         </is>
       </c>
       <c r="I222" t="n">
@@ -13090,7 +13530,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" t="n">
+        <v>7</v>
+      </c>
       <c r="N222" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13122,7 +13564,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>72+858</t>
+          <t>79+709</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -13130,7 +13572,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>4.853408, -73.243358</t>
+          <t>4.841408, -73.216358</t>
         </is>
       </c>
       <c r="I223" t="n">
@@ -13147,7 +13589,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
+      <c r="M223" t="n">
+        <v>7</v>
+      </c>
       <c r="N223" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13179,7 +13623,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>73+822</t>
+          <t>80+674</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -13187,7 +13631,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>4.850306, -73.240161</t>
+          <t>4.838306, -73.213161</t>
         </is>
       </c>
       <c r="I224" t="n">
@@ -13204,7 +13648,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
+      <c r="M224" t="n">
+        <v>7</v>
+      </c>
       <c r="N224" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13236,7 +13682,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>74+788</t>
+          <t>81+639</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -13244,7 +13690,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>4.849219, -73.234293</t>
+          <t>4.837219, -73.207293</t>
         </is>
       </c>
       <c r="I225" t="n">
@@ -13261,7 +13707,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
+      <c r="M225" t="n">
+        <v>7</v>
+      </c>
       <c r="N225" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13293,7 +13741,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>75+753</t>
+          <t>82+604</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -13301,7 +13749,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>4.847260, -73.230662</t>
+          <t>4.835260, -73.203662</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -13318,7 +13766,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
+      <c r="M226" t="n">
+        <v>7</v>
+      </c>
       <c r="N226" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13350,7 +13800,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>76+718</t>
+          <t>83+569</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -13358,7 +13808,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>4.844846, -73.226740</t>
+          <t>4.832846, -73.199740</t>
         </is>
       </c>
       <c r="I227" t="n">
@@ -13375,7 +13825,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>7</v>
+      </c>
       <c r="N227" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13407,7 +13859,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>77+683</t>
+          <t>84+534</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -13415,7 +13867,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>4.844236, -73.225117</t>
+          <t>4.832236, -73.198117</t>
         </is>
       </c>
       <c r="I228" t="n">
@@ -13432,7 +13884,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
+      <c r="M228" t="n">
+        <v>7</v>
+      </c>
       <c r="N228" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13464,7 +13918,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>78+648</t>
+          <t>85+499</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -13472,7 +13926,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>4.842286, -73.219679</t>
+          <t>4.830286, -73.192679</t>
         </is>
       </c>
       <c r="I229" t="n">
@@ -13489,7 +13943,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>7</v>
+      </c>
       <c r="N229" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13521,7 +13977,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>79+612</t>
+          <t>86+464</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -13529,7 +13985,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>4.839687, -73.215485</t>
+          <t>4.827687, -73.188485</t>
         </is>
       </c>
       <c r="I230" t="n">
@@ -13546,7 +14002,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>7</v>
+      </c>
       <c r="N230" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13578,7 +14036,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>80+578</t>
+          <t>87+429</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -13586,7 +14044,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>4.838533, -73.211614</t>
+          <t>4.826533, -73.184614</t>
         </is>
       </c>
       <c r="I231" t="n">
@@ -13603,7 +14061,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>7</v>
+      </c>
       <c r="N231" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13635,7 +14095,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>81+543</t>
+          <t>88+394</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -13643,7 +14103,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>4.836313, -73.208518</t>
+          <t>4.824313, -73.181518</t>
         </is>
       </c>
       <c r="I232" t="n">
@@ -13660,7 +14120,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>7</v>
+      </c>
       <c r="N232" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13692,7 +14154,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>82+507</t>
+          <t>89+359</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -13700,7 +14162,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>4.834633, -73.204473</t>
+          <t>4.822633, -73.177473</t>
         </is>
       </c>
       <c r="I233" t="n">
@@ -13717,7 +14179,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>7</v>
+      </c>
       <c r="N233" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13749,7 +14213,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>83+472</t>
+          <t>90+324</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -13757,7 +14221,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>4.834420, -73.201620</t>
+          <t>4.822420, -73.174620</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -13774,7 +14238,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>7</v>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13806,7 +14272,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>84+438</t>
+          <t>91+289</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -13814,7 +14280,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>4.831037, -73.198476</t>
+          <t>4.819037, -73.171476</t>
         </is>
       </c>
       <c r="I235" t="n">
@@ -13831,7 +14297,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>7</v>
+      </c>
       <c r="N235" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13863,7 +14331,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>85+402</t>
+          <t>92+254</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -13871,7 +14339,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>4.830540, -73.193472</t>
+          <t>4.819131, -73.164106</t>
         </is>
       </c>
       <c r="I236" t="n">
@@ -13888,7 +14356,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
+      <c r="M236" t="n">
+        <v>7</v>
+      </c>
       <c r="N236" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13920,7 +14390,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>86+368</t>
+          <t>93+219</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -13928,7 +14398,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>4.828384, -73.189829</t>
+          <t>4.817610, -73.157927</t>
         </is>
       </c>
       <c r="I237" t="n">
@@ -13945,7 +14415,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>7</v>
+      </c>
       <c r="N237" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -13977,7 +14449,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>87+333</t>
+          <t>94+184</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -13985,7 +14457,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>4.827677, -73.186135</t>
+          <t>4.817536, -73.151698</t>
         </is>
       </c>
       <c r="I238" t="n">
@@ -14002,7 +14474,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>7</v>
+      </c>
       <c r="N238" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14034,7 +14508,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>88+297</t>
+          <t>95+149</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -14042,7 +14516,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>4.825796, -73.181166</t>
+          <t>4.816289, -73.144194</t>
         </is>
       </c>
       <c r="I239" t="n">
@@ -14059,7 +14533,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>7</v>
+      </c>
       <c r="N239" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14091,7 +14567,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>89+263</t>
+          <t>96+114</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -14099,7 +14575,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>4.824651, -73.179320</t>
+          <t>4.815777, -73.139813</t>
         </is>
       </c>
       <c r="I240" t="n">
@@ -14116,7 +14592,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr"/>
+      <c r="M240" t="n">
+        <v>7</v>
+      </c>
       <c r="N240" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14148,7 +14626,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>90+228</t>
+          <t>97+079</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -14156,7 +14634,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>4.823164, -73.174136</t>
+          <t>4.814925, -73.132094</t>
         </is>
       </c>
       <c r="I241" t="n">
@@ -14173,7 +14651,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>7</v>
+      </c>
       <c r="N241" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14205,7 +14685,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>91+192</t>
+          <t>98+044</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -14213,7 +14693,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>4.820234, -73.170230</t>
+          <t>4.812628, -73.125653</t>
         </is>
       </c>
       <c r="I242" t="n">
@@ -14230,7 +14710,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
+      <c r="M242" t="n">
+        <v>7</v>
+      </c>
       <c r="N242" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14262,7 +14744,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>92+157</t>
+          <t>99+009</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -14270,7 +14752,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>4.819746, -73.166001</t>
+          <t>4.812246, -73.121001</t>
         </is>
       </c>
       <c r="I243" t="n">
@@ -14287,7 +14769,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>7</v>
+      </c>
       <c r="N243" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14319,7 +14803,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>93+123</t>
+          <t>99+974</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -14327,7 +14811,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>4.817534, -73.158431</t>
+          <t>4.810034, -73.113431</t>
         </is>
       </c>
       <c r="I244" t="n">
@@ -14344,7 +14828,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>7</v>
+      </c>
       <c r="N244" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14376,7 +14862,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>94+087</t>
+          <t>100+939</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -14384,7 +14870,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>4.816643, -73.151450</t>
+          <t>4.809143, -73.106450</t>
         </is>
       </c>
       <c r="I245" t="n">
@@ -14401,7 +14887,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
+      <c r="M245" t="n">
+        <v>7</v>
+      </c>
       <c r="N245" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14433,7 +14921,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>95+052</t>
+          <t>101+904</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -14441,7 +14929,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>4.816824, -73.145627</t>
+          <t>4.809324, -73.100627</t>
         </is>
       </c>
       <c r="I246" t="n">
@@ -14458,7 +14946,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>7</v>
+      </c>
       <c r="N246" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14486,11 +14976,11 @@
         <v>12</v>
       </c>
       <c r="E247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>96+017</t>
+          <t>102+869</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -14498,7 +14988,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>4.816113, -73.138737</t>
+          <t>4.808613, -73.093737</t>
         </is>
       </c>
       <c r="I247" t="n">
@@ -14515,7 +15005,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>7</v>
+      </c>
       <c r="N247" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14543,11 +15035,11 @@
         <v>12</v>
       </c>
       <c r="E248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>96+982</t>
+          <t>103+834</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -14555,7 +15047,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>4.813019, -73.134284</t>
+          <t>4.805519, -73.089284</t>
         </is>
       </c>
       <c r="I248" t="n">
@@ -14572,7 +15064,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>7</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14600,11 +15094,11 @@
         <v>12</v>
       </c>
       <c r="E249" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>97+948</t>
+          <t>104+799</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -14612,7 +15106,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>4.813514, -73.126130</t>
+          <t>4.806014, -73.081130</t>
         </is>
       </c>
       <c r="I249" t="n">
@@ -14629,7 +15123,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr"/>
+      <c r="M249" t="n">
+        <v>7</v>
+      </c>
       <c r="N249" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14657,11 +15153,11 @@
         <v>12</v>
       </c>
       <c r="E250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>98+913</t>
+          <t>105+764</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -14669,7 +15165,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>4.813002, -73.121362</t>
+          <t>4.805502, -73.076362</t>
         </is>
       </c>
       <c r="I250" t="n">
@@ -14686,7 +15182,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
+      <c r="M250" t="n">
+        <v>7</v>
+      </c>
       <c r="N250" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14714,11 +15212,11 @@
         <v>12</v>
       </c>
       <c r="E251" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>99+877</t>
+          <t>106+729</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -14726,7 +15224,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>4.810926, -73.114870</t>
+          <t>4.803426, -73.069870</t>
         </is>
       </c>
       <c r="I251" t="n">
@@ -14743,7 +15241,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr"/>
+      <c r="M251" t="n">
+        <v>7</v>
+      </c>
       <c r="N251" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14771,11 +15271,11 @@
         <v>12</v>
       </c>
       <c r="E252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>100+843</t>
+          <t>107+694</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -14783,7 +15283,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>4.809365, -73.107709</t>
+          <t>4.801865, -73.062709</t>
         </is>
       </c>
       <c r="I252" t="n">
@@ -14800,7 +15300,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr"/>
+      <c r="M252" t="n">
+        <v>7</v>
+      </c>
       <c r="N252" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14828,11 +15330,11 @@
         <v>12</v>
       </c>
       <c r="E253" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>101+808</t>
+          <t>108+659</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -14840,7 +15342,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>4.808143, -73.102388</t>
+          <t>4.800643, -73.057388</t>
         </is>
       </c>
       <c r="I253" t="n">
@@ -14857,7 +15359,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr"/>
+      <c r="M253" t="n">
+        <v>7</v>
+      </c>
       <c r="N253" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14889,7 +15393,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>102+773</t>
+          <t>109+624</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -14897,7 +15401,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>4.808652, -73.095818</t>
+          <t>4.801152, -73.050818</t>
         </is>
       </c>
       <c r="I254" t="n">
@@ -14914,7 +15418,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>7</v>
+      </c>
       <c r="N254" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -14946,7 +15452,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>103+737</t>
+          <t>110+589</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -14954,7 +15460,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>4.807104, -73.088816</t>
+          <t>4.799604, -73.043816</t>
         </is>
       </c>
       <c r="I255" t="n">
@@ -14971,7 +15477,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
+      <c r="M255" t="n">
+        <v>7</v>
+      </c>
       <c r="N255" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15003,7 +15511,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>104+703</t>
+          <t>111+554</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -15011,7 +15519,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>4.805008, -73.082562</t>
+          <t>4.797508, -73.037562</t>
         </is>
       </c>
       <c r="I256" t="n">
@@ -15028,7 +15536,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>7</v>
+      </c>
       <c r="N256" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15060,7 +15570,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>105+668</t>
+          <t>112+519</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -15068,7 +15578,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>4.805380, -73.077246</t>
+          <t>4.797880, -73.032246</t>
         </is>
       </c>
       <c r="I257" t="n">
@@ -15085,7 +15595,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr"/>
+      <c r="M257" t="n">
+        <v>7</v>
+      </c>
       <c r="N257" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15117,7 +15629,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>106+632</t>
+          <t>113+484</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -15125,7 +15637,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>4.804375, -73.068996</t>
+          <t>4.796875, -73.023996</t>
         </is>
       </c>
       <c r="I258" t="n">
@@ -15142,7 +15654,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr"/>
+      <c r="M258" t="n">
+        <v>7</v>
+      </c>
       <c r="N258" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15174,7 +15688,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>107+597</t>
+          <t>114+449</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -15182,7 +15696,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>4.803032, -73.064091</t>
+          <t>4.795644, -73.019429</t>
         </is>
       </c>
       <c r="I259" t="n">
@@ -15199,7 +15713,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
+      <c r="M259" t="n">
+        <v>7</v>
+      </c>
       <c r="N259" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15231,7 +15747,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>108+563</t>
+          <t>115+414</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -15239,7 +15755,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>4.800226, -73.057452</t>
+          <t>4.793261, -73.014057</t>
         </is>
       </c>
       <c r="I260" t="n">
@@ -15256,7 +15772,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr"/>
+      <c r="M260" t="n">
+        <v>7</v>
+      </c>
       <c r="N260" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15288,7 +15806,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>109+528</t>
+          <t>116+379</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -15296,7 +15814,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>4.800058, -73.049512</t>
+          <t>4.793516, -73.007385</t>
         </is>
       </c>
       <c r="I261" t="n">
@@ -15313,7 +15831,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr"/>
+      <c r="M261" t="n">
+        <v>7</v>
+      </c>
       <c r="N261" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15345,7 +15865,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>110+493</t>
+          <t>117+344</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -15353,7 +15873,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>4.797928, -73.044288</t>
+          <t>4.791808, -73.003429</t>
         </is>
       </c>
       <c r="I262" t="n">
@@ -15370,7 +15890,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr"/>
+      <c r="M262" t="n">
+        <v>7</v>
+      </c>
       <c r="N262" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15402,7 +15924,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>111+458</t>
+          <t>118+309</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -15410,7 +15932,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>4.797203, -73.037746</t>
+          <t>4.791506, -72.998155</t>
         </is>
       </c>
       <c r="I263" t="n">
@@ -15427,7 +15949,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr"/>
+      <c r="M263" t="n">
+        <v>7</v>
+      </c>
       <c r="N263" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15459,7 +15983,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>112+422</t>
+          <t>119+274</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -15467,7 +15991,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>4.796648, -73.032183</t>
+          <t>4.791373, -72.993859</t>
         </is>
       </c>
       <c r="I264" t="n">
@@ -15484,7 +16008,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr"/>
+      <c r="M264" t="n">
+        <v>7</v>
+      </c>
       <c r="N264" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15516,7 +16042,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>113+388</t>
+          <t>120+239</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -15524,7 +16050,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>4.795591, -73.024554</t>
+          <t>4.790739, -72.987498</t>
         </is>
       </c>
       <c r="I265" t="n">
@@ -15541,7 +16067,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr"/>
+      <c r="M265" t="n">
+        <v>7</v>
+      </c>
       <c r="N265" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15573,7 +16101,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>114+353</t>
+          <t>121+204</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -15581,7 +16109,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>4.794408, -73.020056</t>
+          <t>4.789908, -72.984056</t>
         </is>
       </c>
       <c r="I266" t="n">
@@ -15598,7 +16126,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr"/>
+      <c r="M266" t="n">
+        <v>7</v>
+      </c>
       <c r="N266" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15630,7 +16160,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>115+317</t>
+          <t>122+169</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -15638,7 +16168,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>4.793208, -73.015336</t>
+          <t>4.788708, -72.979336</t>
         </is>
       </c>
       <c r="I267" t="n">
@@ -15655,7 +16185,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr"/>
+      <c r="M267" t="n">
+        <v>7</v>
+      </c>
       <c r="N267" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15687,7 +16219,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>116+282</t>
+          <t>123+134</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -15695,7 +16227,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>4.794412, -73.008623</t>
+          <t>4.789912, -72.972623</t>
         </is>
       </c>
       <c r="I268" t="n">
@@ -15712,7 +16244,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr"/>
+      <c r="M268" t="n">
+        <v>7</v>
+      </c>
       <c r="N268" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15744,7 +16278,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>117+248</t>
+          <t>124+099</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -15752,7 +16286,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>4.793187, -73.003865</t>
+          <t>4.788687, -72.967865</t>
         </is>
       </c>
       <c r="I269" t="n">
@@ -15769,7 +16303,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr"/>
+      <c r="M269" t="n">
+        <v>7</v>
+      </c>
       <c r="N269" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15801,7 +16337,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>118+212</t>
+          <t>125+064</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -15809,7 +16345,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>4.792300, -72.999448</t>
+          <t>4.787800, -72.963448</t>
         </is>
       </c>
       <c r="I270" t="n">
@@ -15826,7 +16362,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr"/>
+      <c r="M270" t="n">
+        <v>7</v>
+      </c>
       <c r="N270" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15858,7 +16396,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>119+177</t>
+          <t>126+029</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -15866,7 +16404,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>4.792103, -72.994994</t>
+          <t>4.787603, -72.958994</t>
         </is>
       </c>
       <c r="I271" t="n">
@@ -15883,7 +16421,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr"/>
+      <c r="M271" t="n">
+        <v>7</v>
+      </c>
       <c r="N271" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15915,7 +16455,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>120+143</t>
+          <t>126+994</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -15923,7 +16463,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>4.791645, -72.987641</t>
+          <t>4.787145, -72.951641</t>
         </is>
       </c>
       <c r="I272" t="n">
@@ -15940,7 +16480,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>7</v>
+      </c>
       <c r="N272" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -15972,7 +16514,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>121+108</t>
+          <t>127+959</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -15980,7 +16522,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>4.789699, -72.983657</t>
+          <t>4.785199, -72.947657</t>
         </is>
       </c>
       <c r="I273" t="n">
@@ -15997,7 +16539,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>7</v>
+      </c>
       <c r="N273" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16029,7 +16573,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>122+073</t>
+          <t>128+924</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -16037,7 +16581,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>4.790429, -72.979152</t>
+          <t>4.785929, -72.943152</t>
         </is>
       </c>
       <c r="I274" t="n">
@@ -16054,7 +16598,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>7</v>
+      </c>
       <c r="N274" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16086,7 +16632,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>123+038</t>
+          <t>129+889</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -16094,7 +16640,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>4.789271, -72.972659</t>
+          <t>4.784771, -72.936659</t>
         </is>
       </c>
       <c r="I275" t="n">
@@ -16111,7 +16657,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>7</v>
+      </c>
       <c r="N275" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16143,7 +16691,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>124+002</t>
+          <t>130+854</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -16151,7 +16699,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>4.789116, -72.969053</t>
+          <t>4.784616, -72.933053</t>
         </is>
       </c>
       <c r="I276" t="n">
@@ -16168,7 +16716,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>7</v>
+      </c>
       <c r="N276" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16200,7 +16750,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>124+968</t>
+          <t>131+819</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -16208,7 +16758,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>4.787060, -72.962993</t>
+          <t>4.782560, -72.926993</t>
         </is>
       </c>
       <c r="I277" t="n">
@@ -16225,7 +16775,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>7</v>
+      </c>
       <c r="N277" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16257,7 +16809,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>125+933</t>
+          <t>132+784</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -16265,7 +16817,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>4.786596, -72.958137</t>
+          <t>4.782096, -72.922137</t>
         </is>
       </c>
       <c r="I278" t="n">
@@ -16282,7 +16834,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>7</v>
+      </c>
       <c r="N278" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16314,7 +16868,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>126+897</t>
+          <t>133+749</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -16322,7 +16876,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>4.786522, -72.953458</t>
+          <t>4.782022, -72.917458</t>
         </is>
       </c>
       <c r="I279" t="n">
@@ -16339,7 +16893,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>7</v>
+      </c>
       <c r="N279" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16371,7 +16927,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>127+862</t>
+          <t>134+714</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -16379,7 +16935,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>4.785645, -72.948427</t>
+          <t>4.781145, -72.912427</t>
         </is>
       </c>
       <c r="I280" t="n">
@@ -16396,7 +16952,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>7</v>
+      </c>
       <c r="N280" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16428,7 +16986,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>128+827</t>
+          <t>135+679</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -16436,7 +16994,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>4.786039, -72.942826</t>
+          <t>4.781539, -72.906826</t>
         </is>
       </c>
       <c r="I281" t="n">
@@ -16453,7 +17011,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>7</v>
+      </c>
       <c r="N281" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16485,7 +17045,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>129+792</t>
+          <t>136+644</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -16493,7 +17053,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>4.784910, -72.939237</t>
+          <t>4.780410, -72.903237</t>
         </is>
       </c>
       <c r="I282" t="n">
@@ -16510,7 +17070,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr"/>
+      <c r="M282" t="n">
+        <v>7</v>
+      </c>
       <c r="N282" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16538,11 +17100,11 @@
         <v>12</v>
       </c>
       <c r="E283" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>130+757</t>
+          <t>00+579</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -16550,7 +17112,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>4.783104, -72.933409</t>
+          <t>5.098477, -73.717662</t>
         </is>
       </c>
       <c r="I283" t="n">
@@ -16567,7 +17129,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr"/>
+      <c r="M283" t="n">
+        <v>7</v>
+      </c>
       <c r="N283" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16595,11 +17159,11 @@
         <v>12</v>
       </c>
       <c r="E284" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>131+722</t>
+          <t>01+544</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -16607,7 +17171,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>4.782902, -72.928048</t>
+          <t>5.098064, -73.712724</t>
         </is>
       </c>
       <c r="I284" t="n">
@@ -16624,7 +17188,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr"/>
+      <c r="M284" t="n">
+        <v>7</v>
+      </c>
       <c r="N284" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16652,11 +17218,11 @@
         <v>12</v>
       </c>
       <c r="E285" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>132+688</t>
+          <t>02+509</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -16664,7 +17230,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>4.781778, -72.922984</t>
+          <t>5.096729, -73.708083</t>
         </is>
       </c>
       <c r="I285" t="n">
@@ -16681,7 +17247,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr"/>
+      <c r="M285" t="n">
+        <v>7</v>
+      </c>
       <c r="N285" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16709,11 +17277,11 @@
         <v>12</v>
       </c>
       <c r="E286" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>133+653</t>
+          <t>03+474</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -16721,7 +17289,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>4.780934, -72.916986</t>
+          <t>5.095674, -73.702507</t>
         </is>
       </c>
       <c r="I286" t="n">
@@ -16738,7 +17306,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr"/>
+      <c r="M286" t="n">
+        <v>7</v>
+      </c>
       <c r="N286" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16766,11 +17336,11 @@
         <v>12</v>
       </c>
       <c r="E287" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>134+618</t>
+          <t>04+439</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -16778,7 +17348,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>4.782398, -72.911469</t>
+          <t>5.096926, -73.697413</t>
         </is>
       </c>
       <c r="I287" t="n">
@@ -16795,7 +17365,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr"/>
+      <c r="M287" t="n">
+        <v>7</v>
+      </c>
       <c r="N287" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16823,11 +17395,11 @@
         <v>12</v>
       </c>
       <c r="E288" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>135+583</t>
+          <t>05+404</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -16835,7 +17407,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>4.779686, -72.908398</t>
+          <t>5.094003, -73.694764</t>
         </is>
       </c>
       <c r="I288" t="n">
@@ -16852,7 +17424,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr"/>
+      <c r="M288" t="n">
+        <v>7</v>
+      </c>
       <c r="N288" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16880,11 +17454,11 @@
         <v>12</v>
       </c>
       <c r="E289" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>136+548</t>
+          <t>06+369</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -16892,7 +17466,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>4.780238, -72.903131</t>
+          <t>5.094344, -73.689920</t>
         </is>
       </c>
       <c r="I289" t="n">
@@ -16909,7 +17483,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr"/>
+      <c r="M289" t="n">
+        <v>7</v>
+      </c>
       <c r="N289" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -16966,7 +17542,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr"/>
+      <c r="M290" t="n">
+        <v>4</v>
+      </c>
       <c r="N290" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17023,7 +17601,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr"/>
+      <c r="M291" t="n">
+        <v>4</v>
+      </c>
       <c r="N291" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17080,7 +17660,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr"/>
+      <c r="M292" t="n">
+        <v>4</v>
+      </c>
       <c r="N292" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17137,7 +17719,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M293" t="inlineStr"/>
+      <c r="M293" t="n">
+        <v>4</v>
+      </c>
       <c r="N293" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17194,7 +17778,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr"/>
+      <c r="M294" t="n">
+        <v>4</v>
+      </c>
       <c r="N294" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17251,7 +17837,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr"/>
+      <c r="M295" t="n">
+        <v>4</v>
+      </c>
       <c r="N295" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17308,7 +17896,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr"/>
+      <c r="M296" t="n">
+        <v>4</v>
+      </c>
       <c r="N296" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17365,7 +17955,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr"/>
+      <c r="M297" t="n">
+        <v>4</v>
+      </c>
       <c r="N297" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17422,7 +18014,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr"/>
+      <c r="M298" t="n">
+        <v>4</v>
+      </c>
       <c r="N298" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17479,7 +18073,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr"/>
+      <c r="M299" t="n">
+        <v>4</v>
+      </c>
       <c r="N299" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17536,7 +18132,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr"/>
+      <c r="M300" t="n">
+        <v>4</v>
+      </c>
       <c r="N300" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17593,7 +18191,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr"/>
+      <c r="M301" t="n">
+        <v>4</v>
+      </c>
       <c r="N301" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17625,7 +18225,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>12+561</t>
+          <t>13+931</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -17633,7 +18233,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>5.090082, -73.660770</t>
+          <t>5.088882, -73.654170</t>
         </is>
       </c>
       <c r="I302" t="n">
@@ -17650,7 +18250,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M302" t="inlineStr"/>
+      <c r="M302" t="n">
+        <v>4</v>
+      </c>
       <c r="N302" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17682,7 +18284,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>23+980</t>
+          <t>25+351</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -17690,7 +18292,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>5.076021, -73.603893</t>
+          <t>5.071221, -73.595493</t>
         </is>
       </c>
       <c r="I303" t="n">
@@ -17707,7 +18309,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr"/>
+      <c r="M303" t="n">
+        <v>4</v>
+      </c>
       <c r="N303" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17739,7 +18343,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>35+399</t>
+          <t>36+770</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -17747,7 +18351,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>5.035925, -73.533471</t>
+          <t>5.031125, -73.525071</t>
         </is>
       </c>
       <c r="I304" t="n">
@@ -17764,7 +18368,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr"/>
+      <c r="M304" t="n">
+        <v>4</v>
+      </c>
       <c r="N304" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17796,7 +18402,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>46+819</t>
+          <t>48+189</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -17804,7 +18410,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>4.993261, -73.459866</t>
+          <t>4.984861, -73.447266</t>
         </is>
       </c>
       <c r="I305" t="n">
@@ -17821,7 +18427,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr"/>
+      <c r="M305" t="n">
+        <v>4</v>
+      </c>
       <c r="N305" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17853,7 +18461,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>58+238</t>
+          <t>59+608</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -17861,7 +18469,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>4.922977, -73.355512</t>
+          <t>4.914577, -73.342912</t>
         </is>
       </c>
       <c r="I306" t="n">
@@ -17878,7 +18486,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr"/>
+      <c r="M306" t="n">
+        <v>4</v>
+      </c>
       <c r="N306" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17910,7 +18520,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69+657</t>
+          <t>71+027</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -17918,7 +18528,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>4.859109, -73.255973</t>
+          <t>4.856709, -73.250573</t>
         </is>
       </c>
       <c r="I307" t="n">
@@ -17935,7 +18545,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr"/>
+      <c r="M307" t="n">
+        <v>4</v>
+      </c>
       <c r="N307" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -17967,7 +18579,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>81+076</t>
+          <t>82+446</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -17975,7 +18587,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>4.839174, -73.211278</t>
+          <t>4.836774, -73.205878</t>
         </is>
       </c>
       <c r="I308" t="n">
@@ -17992,7 +18604,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr"/>
+      <c r="M308" t="n">
+        <v>4</v>
+      </c>
       <c r="N308" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18024,7 +18638,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>92+495</t>
+          <t>93+866</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -18032,7 +18646,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>4.819939, -73.163333</t>
+          <t>4.818439, -73.154333</t>
         </is>
       </c>
       <c r="I309" t="n">
@@ -18049,7 +18663,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr"/>
+      <c r="M309" t="n">
+        <v>4</v>
+      </c>
       <c r="N309" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18081,7 +18697,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>103+914</t>
+          <t>105+285</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -18089,7 +18705,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>4.805921, -73.088449</t>
+          <t>4.804421, -73.079449</t>
         </is>
       </c>
       <c r="I310" t="n">
@@ -18106,7 +18722,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr"/>
+      <c r="M310" t="n">
+        <v>4</v>
+      </c>
       <c r="N310" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18138,7 +18756,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>115+334</t>
+          <t>116+704</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -18146,7 +18764,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>4.794911, -73.013745</t>
+          <t>4.794011, -73.006545</t>
         </is>
       </c>
       <c r="I311" t="n">
@@ -18163,7 +18781,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr"/>
+      <c r="M311" t="n">
+        <v>4</v>
+      </c>
       <c r="N311" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18195,7 +18815,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>126+753</t>
+          <t>128+123</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -18203,7 +18823,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>4.786981, -72.952990</t>
+          <t>4.786081, -72.945790</t>
         </is>
       </c>
       <c r="I312" t="n">
@@ -18220,7 +18840,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr"/>
+      <c r="M312" t="n">
+        <v>4</v>
+      </c>
       <c r="N312" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18252,7 +18874,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>01+142</t>
+          <t>02+512</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -18260,7 +18882,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>5.097873, -73.714205</t>
+          <t>5.096673, -73.707605</t>
         </is>
       </c>
       <c r="I313" t="n">
@@ -18277,7 +18899,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr"/>
+      <c r="M313" t="n">
+        <v>4</v>
+      </c>
       <c r="N313" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18309,7 +18933,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>11+158</t>
+          <t>16+639</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -18317,7 +18941,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>5.091391, -73.665547</t>
+          <t>5.086591, -73.639147</t>
         </is>
       </c>
       <c r="I314" t="n">
@@ -18334,7 +18958,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr"/>
+      <c r="M314" t="n">
+        <v>4</v>
+      </c>
       <c r="N314" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18362,11 +18988,11 @@
         <v>16</v>
       </c>
       <c r="E315" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>30+734</t>
+          <t>36+215</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -18374,7 +19000,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>5.052464, -73.562551</t>
+          <t>5.033264, -73.528951</t>
         </is>
       </c>
       <c r="I315" t="n">
@@ -18391,7 +19017,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr"/>
+      <c r="M315" t="n">
+        <v>4</v>
+      </c>
       <c r="N315" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18423,7 +19051,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>50+310</t>
+          <t>55+791</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -18431,7 +19059,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>4.971684, -73.426834</t>
+          <t>4.938084, -73.376434</t>
         </is>
       </c>
       <c r="I316" t="n">
@@ -18448,7 +19076,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr"/>
+      <c r="M316" t="n">
+        <v>4</v>
+      </c>
       <c r="N316" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18480,7 +19110,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69+885</t>
+          <t>75+367</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -18488,7 +19118,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>4.857070, -73.253649</t>
+          <t>4.847470, -73.232049</t>
         </is>
       </c>
       <c r="I317" t="n">
@@ -18505,7 +19135,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr"/>
+      <c r="M317" t="n">
+        <v>4</v>
+      </c>
       <c r="N317" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18537,7 +19169,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>89+461</t>
+          <t>94+942</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -18545,7 +19177,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>4.822113, -73.178582</t>
+          <t>4.814871, -73.147553</t>
         </is>
       </c>
       <c r="I318" t="n">
@@ -18562,7 +19194,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr"/>
+      <c r="M318" t="n">
+        <v>4</v>
+      </c>
       <c r="N318" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18594,7 +19228,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>109+037</t>
+          <t>114+518</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -18602,7 +19236,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>4.799539, -73.053408</t>
+          <t>4.793682, -73.017836</t>
         </is>
       </c>
       <c r="I319" t="n">
@@ -18619,7 +19253,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr"/>
+      <c r="M319" t="n">
+        <v>4</v>
+      </c>
       <c r="N319" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18651,7 +19287,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>128+612</t>
+          <t>134+094</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -18659,7 +19295,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>4.785411, -72.945346</t>
+          <t>4.781811, -72.916546</t>
         </is>
       </c>
       <c r="I320" t="n">
@@ -18676,7 +19312,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr"/>
+      <c r="M320" t="n">
+        <v>4</v>
+      </c>
       <c r="N320" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18708,7 +19346,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>42+479</t>
+          <t>35+628</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -18716,7 +19354,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>5.011810, -73.490474</t>
+          <t>5.035810, -73.532474</t>
         </is>
       </c>
       <c r="I321" t="n">
@@ -18733,7 +19371,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr"/>
+      <c r="M321" t="n">
+        <v>7</v>
+      </c>
       <c r="N321" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18765,7 +19405,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>110+994</t>
+          <t>104+143</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -18773,7 +19413,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>4.799398, -73.041047</t>
+          <t>4.806898, -73.086047</t>
         </is>
       </c>
       <c r="I322" t="n">
@@ -18790,7 +19430,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr"/>
+      <c r="M322" t="n">
+        <v>7</v>
+      </c>
       <c r="N322" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18822,7 +19464,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>36+998</t>
+          <t>39+739</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -18830,7 +19472,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>5.031470, -73.523089</t>
+          <t>5.021870, -73.506289</t>
         </is>
       </c>
       <c r="I323" t="n">
@@ -18847,7 +19489,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr"/>
+      <c r="M323" t="n">
+        <v>4</v>
+      </c>
       <c r="N323" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18879,7 +19523,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>105+513</t>
+          <t>108+254</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -18887,7 +19531,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>4.805154, -73.077004</t>
+          <t>4.802154, -73.059004</t>
         </is>
       </c>
       <c r="I324" t="n">
@@ -18904,7 +19548,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr"/>
+      <c r="M324" t="n">
+        <v>4</v>
+      </c>
       <c r="N324" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -18936,7 +19582,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>03+733</t>
+          <t>06+473</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -18944,7 +19590,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>5.097339, -73.702533</t>
+          <t>5.094939, -73.689333</t>
         </is>
       </c>
       <c r="I325" t="n">
@@ -18993,7 +19639,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>08+458</t>
+          <t>11+199</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -19001,7 +19647,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>5.092857, -73.680422</t>
+          <t>5.090457, -73.667222</t>
         </is>
       </c>
       <c r="I326" t="n">
@@ -19050,7 +19696,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>13+183</t>
+          <t>15+924</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -19058,7 +19704,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>5.087757, -73.657209</t>
+          <t>5.085357, -73.644009</t>
         </is>
       </c>
       <c r="I327" t="n">
@@ -19107,7 +19753,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>17+908</t>
+          <t>20+649</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -19115,7 +19761,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>5.083335, -73.634294</t>
+          <t>5.080935, -73.621094</t>
         </is>
       </c>
       <c r="I328" t="n">
@@ -19164,7 +19810,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>22+634</t>
+          <t>25+374</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -19172,7 +19818,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>5.080297, -73.611889</t>
+          <t>5.071235, -73.595358</t>
         </is>
       </c>
       <c r="I329" t="n">
@@ -19221,7 +19867,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>27+359</t>
+          <t>30+099</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -19229,7 +19875,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>5.063577, -73.581534</t>
+          <t>5.053977, -73.564734</t>
         </is>
       </c>
       <c r="I330" t="n">
@@ -19274,11 +19920,11 @@
         <v>16</v>
       </c>
       <c r="E331" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>32+084</t>
+          <t>34+825</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -19286,7 +19932,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>5.046965, -73.552973</t>
+          <t>5.037365, -73.536173</t>
         </is>
       </c>
       <c r="I331" t="n">
@@ -19335,7 +19981,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>36+809</t>
+          <t>39+550</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -19343,7 +19989,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>5.030210, -73.525266</t>
+          <t>5.020610, -73.508466</t>
         </is>
       </c>
       <c r="I332" t="n">
@@ -19392,7 +20038,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>41+534</t>
+          <t>44+275</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -19400,7 +20046,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>5.014902, -73.496442</t>
+          <t>5.005302, -73.479642</t>
         </is>
       </c>
       <c r="I333" t="n">
@@ -19449,7 +20095,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>46+259</t>
+          <t>49+000</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -19457,7 +20103,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>4.997413, -73.464047</t>
+          <t>4.980613, -73.438847</t>
         </is>
       </c>
       <c r="I334" t="n">
@@ -19506,7 +20152,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>50+985</t>
+          <t>53+725</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -19514,7 +20160,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>4.967899, -73.422350</t>
+          <t>4.951099, -73.397150</t>
         </is>
       </c>
       <c r="I335" t="n">
@@ -19563,7 +20209,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>55+710</t>
+          <t>58+450</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -19571,7 +20217,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>4.938944, -73.377608</t>
+          <t>4.922144, -73.352408</t>
         </is>
       </c>
       <c r="I336" t="n">
@@ -19620,7 +20266,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>60+435</t>
+          <t>63+176</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -19628,7 +20274,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>4.909432, -73.333375</t>
+          <t>4.892632, -73.308175</t>
         </is>
       </c>
       <c r="I337" t="n">
@@ -19677,7 +20323,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>65+160</t>
+          <t>67+901</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -19685,7 +20331,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>4.881597, -73.289666</t>
+          <t>4.864797, -73.264466</t>
         </is>
       </c>
       <c r="I338" t="n">
@@ -19734,7 +20380,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>69+885</t>
+          <t>72+626</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -19742,7 +20388,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>4.856636, -73.254041</t>
+          <t>4.851836, -73.243241</t>
         </is>
       </c>
       <c r="I339" t="n">
@@ -19791,7 +20437,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>74+610</t>
+          <t>77+351</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -19799,7 +20445,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>4.848619, -73.235740</t>
+          <t>4.843819, -73.224940</t>
         </is>
       </c>
       <c r="I340" t="n">
@@ -19848,7 +20494,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>79+336</t>
+          <t>82+076</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -19856,7 +20502,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>4.839890, -73.216970</t>
+          <t>4.835090, -73.206170</t>
         </is>
       </c>
       <c r="I341" t="n">
@@ -19905,7 +20551,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>84+061</t>
+          <t>86+801</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -19913,7 +20559,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>4.832353, -73.199898</t>
+          <t>4.827553, -73.189098</t>
         </is>
       </c>
       <c r="I342" t="n">
@@ -19962,7 +20608,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>88+786</t>
+          <t>91+527</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -19970,7 +20616,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>4.823197, -73.180814</t>
+          <t>4.818511, -73.169559</t>
         </is>
       </c>
       <c r="I343" t="n">
@@ -20019,7 +20665,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>93+511</t>
+          <t>96+252</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -20027,7 +20673,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>4.817963, -73.156200</t>
+          <t>4.814963, -73.138200</t>
         </is>
       </c>
       <c r="I344" t="n">
@@ -20076,7 +20722,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>98+236</t>
+          <t>100+977</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -20084,7 +20730,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>4.812031, -73.124386</t>
+          <t>4.809031, -73.106386</t>
         </is>
       </c>
       <c r="I345" t="n">
@@ -20133,7 +20779,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>102+962</t>
+          <t>105+702</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -20141,7 +20787,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>4.808476, -73.094759</t>
+          <t>4.805476, -73.076759</t>
         </is>
       </c>
       <c r="I346" t="n">
@@ -20190,7 +20836,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>107+687</t>
+          <t>110+427</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -20198,7 +20844,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>4.801957, -73.061558</t>
+          <t>4.798957, -73.043558</t>
         </is>
       </c>
       <c r="I347" t="n">
@@ -20247,7 +20893,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>112+412</t>
+          <t>115+152</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -20255,7 +20901,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>4.796403, -73.030603</t>
+          <t>4.793824, -73.013865</t>
         </is>
       </c>
       <c r="I348" t="n">
@@ -20304,7 +20950,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>117+137</t>
+          <t>119+878</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -20312,7 +20958,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>4.793031, -73.005752</t>
+          <t>4.791231, -72.991352</t>
         </is>
       </c>
       <c r="I349" t="n">
@@ -20361,7 +21007,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>121+862</t>
+          <t>124+603</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -20369,7 +21015,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>4.790570, -72.980674</t>
+          <t>4.788770, -72.966274</t>
         </is>
       </c>
       <c r="I350" t="n">
@@ -20418,7 +21064,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>126+587</t>
+          <t>129+328</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -20426,7 +21072,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>4.787991, -72.955200</t>
+          <t>4.786191, -72.940800</t>
         </is>
       </c>
       <c r="I351" t="n">
@@ -20475,7 +21121,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>131+313</t>
+          <t>134+053</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -20483,7 +21129,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>4.782945, -72.929868</t>
+          <t>4.781145, -72.915468</t>
         </is>
       </c>
       <c r="I352" t="n">
@@ -20528,11 +21174,11 @@
         <v>16</v>
       </c>
       <c r="E353" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>136+038</t>
+          <t>01+748</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -20540,7 +21186,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>4.781949, -72.905641</t>
+          <t>5.099766, -73.712007</t>
         </is>
       </c>
       <c r="I353" t="n">
@@ -20589,7 +21235,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>29+690</t>
+          <t>28+320</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -20597,7 +21243,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>5.056535, -73.568416</t>
+          <t>5.061335, -73.576816</t>
         </is>
       </c>
       <c r="I354" t="n">
@@ -20614,7 +21260,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M354" t="inlineStr"/>
+      <c r="M354" t="n">
+        <v>4</v>
+      </c>
       <c r="N354" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -20646,7 +21294,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>75+367</t>
+          <t>73+996</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -20654,7 +21302,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>4.847361, -73.233100</t>
+          <t>4.849761, -73.238500</t>
         </is>
       </c>
       <c r="I355" t="n">
@@ -20671,7 +21319,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M355" t="inlineStr"/>
+      <c r="M355" t="n">
+        <v>4</v>
+      </c>
       <c r="N355" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>
@@ -20703,7 +21353,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>121+043</t>
+          <t>119+673</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -20711,7 +21361,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>4.791229, -72.982774</t>
+          <t>4.792129, -72.989974</t>
         </is>
       </c>
       <c r="I356" t="n">
@@ -20728,7 +21378,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M356" t="inlineStr"/>
+      <c r="M356" t="n">
+        <v>4</v>
+      </c>
       <c r="N356" t="inlineStr">
         <is>
           <t>ACTIVO SINTETICO DE PRUEBA - NO ES INVENTARIO REAL</t>

--- a/BD/ACT_Activos_355_SINTETICO.xlsx
+++ b/BD/ACT_Activos_355_SINTETICO.xlsx
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E124" t="n">
         <v>7</v>
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E125" t="n">
         <v>8</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E126" t="n">
         <v>9</v>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E127" t="n">
         <v>10</v>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E128" t="n">
         <v>7</v>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E129" t="n">
         <v>7</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E130" t="n">
         <v>7</v>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E131" t="n">
         <v>7</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E132" t="n">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E133" t="n">
         <v>8</v>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E134" t="n">
         <v>8</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E135" t="n">
         <v>8</v>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E136" t="n">
         <v>9</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E137" t="n">
         <v>9</v>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E138" t="n">
         <v>9</v>
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E139" t="n">
         <v>9</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E140" t="n">
         <v>10</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E141" t="n">
         <v>10</v>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E142" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E143" t="n">
         <v>10</v>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E144" t="n">
         <v>7</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E145" t="n">
         <v>8</v>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E146" t="n">
         <v>9</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E147" t="n">
         <v>10</v>
@@ -17510,7 +17510,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E290" t="n">
         <v>7</v>
@@ -17569,7 +17569,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E291" t="n">
         <v>7</v>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E292" t="n">
         <v>7</v>
@@ -17687,7 +17687,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E293" t="n">
         <v>8</v>
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E294" t="n">
         <v>8</v>
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E295" t="n">
         <v>8</v>
@@ -17864,7 +17864,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E296" t="n">
         <v>9</v>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E297" t="n">
         <v>9</v>
@@ -17982,7 +17982,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E298" t="n">
         <v>9</v>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E299" t="n">
         <v>10</v>
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E300" t="n">
         <v>10</v>
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E301" t="n">
         <v>10</v>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E302" t="n">
         <v>7</v>
@@ -18277,7 +18277,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E303" t="n">
         <v>7</v>
@@ -18336,7 +18336,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E304" t="n">
         <v>8</v>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E305" t="n">
         <v>8</v>
@@ -18454,7 +18454,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E306" t="n">
         <v>8</v>
@@ -18513,7 +18513,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E307" t="n">
         <v>9</v>
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E308" t="n">
         <v>9</v>
@@ -18631,7 +18631,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E309" t="n">
         <v>9</v>
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E310" t="n">
         <v>10</v>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E311" t="n">
         <v>10</v>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E312" t="n">
         <v>10</v>
@@ -18867,7 +18867,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E313" t="n">
         <v>7</v>
@@ -19339,7 +19339,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E321" t="n">
         <v>8</v>
@@ -19398,7 +19398,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E322" t="n">
         <v>10</v>
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E323" t="n">
         <v>8</v>
@@ -19516,7 +19516,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E324" t="n">
         <v>10</v>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E325" t="n">
         <v>7</v>
@@ -19632,7 +19632,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E326" t="n">
         <v>7</v>
@@ -19689,7 +19689,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E327" t="n">
         <v>7</v>
@@ -19746,7 +19746,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E328" t="n">
         <v>7</v>
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E329" t="n">
         <v>7</v>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E330" t="n">
         <v>7</v>
@@ -19917,7 +19917,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E331" t="n">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E332" t="n">
         <v>8</v>
@@ -20031,7 +20031,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E333" t="n">
         <v>8</v>
@@ -20088,7 +20088,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E334" t="n">
         <v>8</v>
@@ -20145,7 +20145,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E335" t="n">
         <v>8</v>
@@ -20202,7 +20202,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E336" t="n">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E337" t="n">
         <v>8</v>
@@ -20316,7 +20316,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E338" t="n">
         <v>8</v>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E339" t="n">
         <v>9</v>
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E340" t="n">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E341" t="n">
         <v>9</v>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E342" t="n">
         <v>9</v>
@@ -20601,7 +20601,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E343" t="n">
         <v>9</v>
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E344" t="n">
         <v>9</v>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E345" t="n">
         <v>9</v>
@@ -20772,7 +20772,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E346" t="n">
         <v>10</v>
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E347" t="n">
         <v>10</v>
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E348" t="n">
         <v>10</v>
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E349" t="n">
         <v>10</v>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E350" t="n">
         <v>10</v>
@@ -21057,7 +21057,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E351" t="n">
         <v>10</v>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E352" t="n">
         <v>10</v>
@@ -21171,7 +21171,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E353" t="n">
         <v>7</v>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E354" t="n">
         <v>7</v>
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E355" t="n">
         <v>9</v>
@@ -21346,7 +21346,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E356" t="n">
         <v>10</v>
